--- a/resources/excel_templates/gb_t_32151_34_2024_appendix_b_v5.xlsx
+++ b/resources/excel_templates/gb_t_32151_34_2024_appendix_b_v5.xlsx
@@ -2640,7 +2640,7 @@
       <c r="L19" s="45" t="n"/>
       <c r="M19" s="43" t="n"/>
     </row>
-    <row r="20" ht="34" customHeight="45" s="42">
+    <row r="20" ht="45" customHeight="1" s="42">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>燃料输入规则 V5：含碳量来源“计算值”表示按热值计算，“实测值”表示直接实测，“直接计算值”表示直接计算含碳量。
